--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>5714961</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>0.00920000020414591</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>2042453</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>3027894</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>3819544</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>29363690</v>
+        <v>53028172</v>
       </c>
       <c r="C2715" t="n">
-        <v>0.00980000011622906</v>
+        <v>0.00939999986439943</v>
       </c>
       <c r="D2715" t="n">
-        <v>0.00920000020414591</v>
+        <v>0.00760000012814999</v>
       </c>
       <c r="E2715" t="n">
-        <v>0.00920000020414591</v>
+        <v>0.00779999978840351</v>
       </c>
       <c r="F2715" t="n">
-        <v>0.00920000020414591</v>
+        <v>0.00899999961256981</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>25889575</v>
+        <v>29363690</v>
       </c>
       <c r="C2716" t="n">
-        <v>0.00939999986439943</v>
+        <v>0.00980000011622906</v>
       </c>
       <c r="D2716" t="n">
-        <v>0.00839999970048666</v>
+        <v>0.00920000020414591</v>
       </c>
       <c r="E2716" t="n">
         <v>0.00920000020414591</v>
       </c>
       <c r="F2716" t="n">
-        <v>0.00839999970048666</v>
+        <v>0.00920000020414591</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>18657858</v>
+        <v>25889575</v>
       </c>
       <c r="C2717" t="n">
+        <v>0.00939999986439943</v>
+      </c>
+      <c r="D2717" t="n">
+        <v>0.00839999970048666</v>
+      </c>
+      <c r="E2717" t="n">
         <v>0.00920000020414591</v>
       </c>
-      <c r="D2717" t="n">
-        <v>0.00820000004023314</v>
-      </c>
-      <c r="E2717" t="n">
+      <c r="F2717" t="n">
         <v>0.00839999970048666</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>0.00879999995231628</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,19 +62865,19 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>6726347</v>
+        <v>18657858</v>
       </c>
       <c r="C2718" t="n">
-        <v>0.00899999961256981</v>
+        <v>0.00920000020414591</v>
       </c>
       <c r="D2718" t="n">
-        <v>0.00860000029206276</v>
+        <v>0.00820000004023314</v>
       </c>
       <c r="E2718" t="n">
-        <v>0.00879999995231628</v>
+        <v>0.00839999970048666</v>
       </c>
       <c r="F2718" t="n">
         <v>0.00879999995231628</v>
@@ -62888,19 +62888,19 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>5714961</v>
+        <v>6726347</v>
       </c>
       <c r="C2719" t="n">
-        <v>0.00920000020414591</v>
+        <v>0.00899999961256981</v>
       </c>
       <c r="D2719" t="n">
         <v>0.00860000029206276</v>
       </c>
       <c r="E2719" t="n">
-        <v>0.00899999961256981</v>
+        <v>0.00879999995231628</v>
       </c>
       <c r="F2719" t="n">
         <v>0.00879999995231628</v>
@@ -62911,13 +62911,13 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>2042453</v>
+        <v>5714961</v>
       </c>
       <c r="C2720" t="n">
-        <v>0.00899999961256981</v>
+        <v>0.00920000020414591</v>
       </c>
       <c r="D2720" t="n">
         <v>0.00860000029206276</v>
@@ -62926,7 +62926,7 @@
         <v>0.00899999961256981</v>
       </c>
       <c r="F2720" t="n">
-        <v>0.00860000029206276</v>
+        <v>0.00879999995231628</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>3027894</v>
+        <v>2042453</v>
       </c>
       <c r="C2721" t="n">
-        <v>0.00879999995231628</v>
+        <v>0.00899999961256981</v>
       </c>
       <c r="D2721" t="n">
         <v>0.00860000029206276</v>
       </c>
       <c r="E2721" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="F2721" t="n">
         <v>0.00860000029206276</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>0.00879999995231628</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>3819544</v>
+        <v>3027894</v>
       </c>
       <c r="C2722" t="n">
-        <v>0.00899999961256981</v>
+        <v>0.00879999995231628</v>
       </c>
       <c r="D2722" t="n">
         <v>0.00860000029206276</v>
       </c>
       <c r="E2722" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="F2722" t="n">
         <v>0.00879999995231628</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>3103744</v>
+      </c>
+      <c r="C2723" t="n">
         <v>0.00899999961256981</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="D2723" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>0.00839999970048666</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>1348111</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>634</v>
       </c>
       <c r="G2" t="n">
-        <v>580.39599609375</v>
+        <v>580.396057128906</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>634</v>
       </c>
       <c r="G3" t="n">
-        <v>580.39599609375</v>
+        <v>580.396057128906</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>471.399993896484</v>
       </c>
       <c r="G14" t="n">
-        <v>431.543670654297</v>
+        <v>431.543640136719</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>529</v>
       </c>
       <c r="G21" t="n">
-        <v>484.273651123047</v>
+        <v>484.273620605469</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>448.571075439453</v>
+        <v>448.571044921875</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>559</v>
       </c>
       <c r="G31" t="n">
-        <v>511.737182617188</v>
+        <v>511.737152099609</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>594.5</v>
       </c>
       <c r="G33" t="n">
-        <v>544.235717773438</v>
+        <v>544.235656738281</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>616</v>
       </c>
       <c r="G37" t="n">
-        <v>563.917846679688</v>
+        <v>563.917907714844</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>605</v>
       </c>
       <c r="G40" t="n">
-        <v>553.847961425781</v>
+        <v>553.847900390625</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>606.5</v>
       </c>
       <c r="G43" t="n">
-        <v>555.221069335938</v>
+        <v>555.221130371094</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>605</v>
       </c>
       <c r="G49" t="n">
-        <v>553.847961425781</v>
+        <v>553.847900390625</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>644</v>
       </c>
       <c r="G55" t="n">
-        <v>589.550476074219</v>
+        <v>589.550537109375</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>647.5</v>
       </c>
       <c r="G56" t="n">
-        <v>592.754577636719</v>
+        <v>592.754638671875</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>640</v>
       </c>
       <c r="G57" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>630.5</v>
       </c>
       <c r="G62" t="n">
-        <v>577.19189453125</v>
+        <v>577.191955566406</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>625</v>
       </c>
       <c r="G64" t="n">
-        <v>572.156921386719</v>
+        <v>572.156982421875</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>632</v>
       </c>
       <c r="G65" t="n">
-        <v>578.565124511719</v>
+        <v>578.565063476562</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>626</v>
       </c>
       <c r="G67" t="n">
-        <v>573.072387695312</v>
+        <v>573.072448730469</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>634</v>
       </c>
       <c r="G69" t="n">
-        <v>580.39599609375</v>
+        <v>580.396057128906</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>638.5</v>
       </c>
       <c r="G72" t="n">
-        <v>584.515502929688</v>
+        <v>584.515563964844</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>635.5</v>
       </c>
       <c r="G73" t="n">
-        <v>581.769226074219</v>
+        <v>581.769165039062</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>626.5</v>
       </c>
       <c r="G74" t="n">
-        <v>573.530151367188</v>
+        <v>573.530090332031</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>640</v>
       </c>
       <c r="G76" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>640</v>
       </c>
       <c r="G77" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>635.5</v>
       </c>
       <c r="G79" t="n">
-        <v>581.769226074219</v>
+        <v>581.769165039062</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>640</v>
       </c>
       <c r="G81" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>662.5</v>
       </c>
       <c r="G93" t="n">
-        <v>606.486328125</v>
+        <v>606.486389160156</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -71248,6 +71248,32 @@
         <v>0.00879999995231628</v>
       </c>
       <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>3940139</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="H2727" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -71277,6 +71277,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>1972647</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>634</v>
       </c>
       <c r="G2" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>634</v>
       </c>
       <c r="G3" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>471.399993896484</v>
       </c>
       <c r="G14" t="n">
-        <v>431.543640136719</v>
+        <v>431.543670654297</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>529</v>
       </c>
       <c r="G21" t="n">
-        <v>484.273620605469</v>
+        <v>484.273651123047</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>448.571044921875</v>
+        <v>448.571075439453</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>559</v>
       </c>
       <c r="G31" t="n">
-        <v>511.737152099609</v>
+        <v>511.737182617188</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>594.5</v>
       </c>
       <c r="G33" t="n">
-        <v>544.235656738281</v>
+        <v>544.235717773438</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>616</v>
       </c>
       <c r="G37" t="n">
-        <v>563.917907714844</v>
+        <v>563.917846679688</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>605</v>
       </c>
       <c r="G40" t="n">
-        <v>553.847900390625</v>
+        <v>553.847961425781</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>606.5</v>
       </c>
       <c r="G43" t="n">
-        <v>555.221130371094</v>
+        <v>555.221069335938</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>605</v>
       </c>
       <c r="G49" t="n">
-        <v>553.847900390625</v>
+        <v>553.847961425781</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>644</v>
       </c>
       <c r="G55" t="n">
-        <v>589.550537109375</v>
+        <v>589.550476074219</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>647.5</v>
       </c>
       <c r="G56" t="n">
-        <v>592.754638671875</v>
+        <v>592.754577636719</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>640</v>
       </c>
       <c r="G57" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>630.5</v>
       </c>
       <c r="G62" t="n">
-        <v>577.191955566406</v>
+        <v>577.19189453125</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>625</v>
       </c>
       <c r="G64" t="n">
-        <v>572.156982421875</v>
+        <v>572.156921386719</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>632</v>
       </c>
       <c r="G65" t="n">
-        <v>578.565063476562</v>
+        <v>578.565124511719</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>626</v>
       </c>
       <c r="G67" t="n">
-        <v>573.072448730469</v>
+        <v>573.072387695312</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>634</v>
       </c>
       <c r="G69" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>638.5</v>
       </c>
       <c r="G72" t="n">
-        <v>584.515563964844</v>
+        <v>584.515502929688</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>635.5</v>
       </c>
       <c r="G73" t="n">
-        <v>581.769165039062</v>
+        <v>581.769226074219</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>626.5</v>
       </c>
       <c r="G74" t="n">
-        <v>573.530090332031</v>
+        <v>573.530151367188</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>640</v>
       </c>
       <c r="G76" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>640</v>
       </c>
       <c r="G77" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>635.5</v>
       </c>
       <c r="G79" t="n">
-        <v>581.769165039062</v>
+        <v>581.769226074219</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>640</v>
       </c>
       <c r="G81" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>662.5</v>
       </c>
       <c r="G93" t="n">
-        <v>606.486389160156</v>
+        <v>606.486328125</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -71300,6 +71300,32 @@
         <v>0.00879999995231628</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>56626138</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>0.0104000000283122</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>0.00860000029206276</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>0.00879999995231628</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>0.00999999977648258</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>0.00999999977648258</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -71381,6 +71381,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>38725049</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>0.00999999977648258</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>0.00899999961256981</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>0.00939999986439943</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>0.00999999977648258</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>0.00999999977648258</v>
+      </c>
+      <c r="H2732" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>0.0118000004440546</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>0.0120000001043081</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>65847006</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>0.0162000004202127</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>0.0120000001043081</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>0.0120000001043081</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>0.0120000001043081</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>0.0162000004202127</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>95661046</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>0.0146000003442168</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>0.0165999997407198</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>0.0165999997407198</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>0.0149999996647239</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>61392050</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>0.0146000003442168</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>0.0160000007599592</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>0.0160000007599592</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>0.017400000244379</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>90687480</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>0.0182000007480383</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>93478558</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>0.02280000038445</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>0.0186000000685453</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>0.0209999997168779</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -421,7 +421,7 @@
         <v>634</v>
       </c>
       <c r="G2" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>634</v>
       </c>
       <c r="G3" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>471.399993896484</v>
       </c>
       <c r="G14" t="n">
-        <v>431.543640136719</v>
+        <v>431.543670654297</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>529</v>
       </c>
       <c r="G21" t="n">
-        <v>484.273620605469</v>
+        <v>484.273651123047</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>448.571044921875</v>
+        <v>448.571075439453</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>559</v>
       </c>
       <c r="G31" t="n">
-        <v>511.737152099609</v>
+        <v>511.737182617188</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>594.5</v>
       </c>
       <c r="G33" t="n">
-        <v>544.235656738281</v>
+        <v>544.235717773438</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>616</v>
       </c>
       <c r="G37" t="n">
-        <v>563.917907714844</v>
+        <v>563.917846679688</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>605</v>
       </c>
       <c r="G40" t="n">
-        <v>553.847900390625</v>
+        <v>553.847961425781</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>606.5</v>
       </c>
       <c r="G43" t="n">
-        <v>555.221130371094</v>
+        <v>555.221069335938</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>605</v>
       </c>
       <c r="G49" t="n">
-        <v>553.847900390625</v>
+        <v>553.847961425781</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>644</v>
       </c>
       <c r="G55" t="n">
-        <v>589.550537109375</v>
+        <v>589.550476074219</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>647.5</v>
       </c>
       <c r="G56" t="n">
-        <v>592.754638671875</v>
+        <v>592.754577636719</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>640</v>
       </c>
       <c r="G57" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>630.5</v>
       </c>
       <c r="G62" t="n">
-        <v>577.191955566406</v>
+        <v>577.19189453125</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>625</v>
       </c>
       <c r="G64" t="n">
-        <v>572.156982421875</v>
+        <v>572.156921386719</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>632</v>
       </c>
       <c r="G65" t="n">
-        <v>578.565063476562</v>
+        <v>578.565124511719</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>626</v>
       </c>
       <c r="G67" t="n">
-        <v>573.072448730469</v>
+        <v>573.072387695312</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>634</v>
       </c>
       <c r="G69" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>638.5</v>
       </c>
       <c r="G72" t="n">
-        <v>584.515563964844</v>
+        <v>584.515502929688</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>635.5</v>
       </c>
       <c r="G73" t="n">
-        <v>581.769165039062</v>
+        <v>581.769226074219</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>626.5</v>
       </c>
       <c r="G74" t="n">
-        <v>573.530090332031</v>
+        <v>573.530151367188</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>640</v>
       </c>
       <c r="G76" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>640</v>
       </c>
       <c r="G77" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>635.5</v>
       </c>
       <c r="G79" t="n">
-        <v>581.769165039062</v>
+        <v>581.769226074219</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>640</v>
       </c>
       <c r="G81" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>662.5</v>
       </c>
       <c r="G93" t="n">
-        <v>606.486389160156</v>
+        <v>606.486328125</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -71664,6 +71664,32 @@
         <v>0.0186000000685453</v>
       </c>
       <c r="H2742" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>36220732</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>0.0189999993890524</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>0.0167999994009733</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="H2743" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -71693,6 +71693,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>46573980</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>0.0164000000804663</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>0.013399999588728</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>0.013399999588728</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>0.0140000004321337</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>0.0140000004321337</v>
+      </c>
+      <c r="H2744" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -79954,6 +79954,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2745">
+      <c r="A2745" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2745" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2745" t="n">
+        <v>0.0149999996647239</v>
+      </c>
+      <c r="D2745" t="n">
+        <v>0.0157999992370605</v>
+      </c>
+      <c r="E2745" t="n">
+        <v>0.0124000003561378</v>
+      </c>
+      <c r="F2745" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="G2745" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="H2745" t="n">
+        <v>42194954</v>
+      </c>
+      <c r="I2745" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>0.0136000001803041</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>0.0142000000923872</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>0.0126000000163913</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>37717302</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>0.0131999999284744</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>0.0136000001803041</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>0.0126000000163913</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>27923719</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>0.013399999588728</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>0.013399999588728</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>0.0120000001043081</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>0.0121999997645617</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>0.0121999997645617</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>32097336</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -80070,6 +80070,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>0.0130000002682209</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>0.013399999588728</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>0.0118000004440546</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>0.0124000003561378</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>0.0124000003561378</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>34221025</v>
+      </c>
+      <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>0.0126000000163913</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>0.0127999996766448</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>0.0118000004440546</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>0.0124000003561378</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>0.0124000003561378</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>30767996</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -80128,6 +80128,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>0.0124000003561378</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>0.0136000001803041</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>0.0120000001043081</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>0.0149999996647239</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>0.0149999996647239</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>29310965</v>
+      </c>
+      <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>634</v>
       </c>
       <c r="G2" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H2" t="n">
         <v>141</v>
@@ -456,7 +456,7 @@
         <v>634</v>
       </c>
       <c r="G3" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H3" t="n">
         <v>82</v>
@@ -775,7 +775,7 @@
         <v>471.399993896484</v>
       </c>
       <c r="G14" t="n">
-        <v>431.543640136719</v>
+        <v>431.543670654297</v>
       </c>
       <c r="H14" t="n">
         <v>535</v>
@@ -978,7 +978,7 @@
         <v>529</v>
       </c>
       <c r="G21" t="n">
-        <v>484.273620605469</v>
+        <v>484.273651123047</v>
       </c>
       <c r="H21" t="n">
         <v>70</v>
@@ -1036,7 +1036,7 @@
         <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>448.571044921875</v>
+        <v>448.571075439453</v>
       </c>
       <c r="H23" t="n">
         <v>79</v>
@@ -1268,7 +1268,7 @@
         <v>559</v>
       </c>
       <c r="G31" t="n">
-        <v>511.737152099609</v>
+        <v>511.737182617188</v>
       </c>
       <c r="H31" t="n">
         <v>324</v>
@@ -1326,7 +1326,7 @@
         <v>594.5</v>
       </c>
       <c r="G33" t="n">
-        <v>544.235656738281</v>
+        <v>544.235717773438</v>
       </c>
       <c r="H33" t="n">
         <v>417</v>
@@ -1442,7 +1442,7 @@
         <v>616</v>
       </c>
       <c r="G37" t="n">
-        <v>563.917907714844</v>
+        <v>563.917846679688</v>
       </c>
       <c r="H37" t="n">
         <v>276</v>
@@ -1529,7 +1529,7 @@
         <v>605</v>
       </c>
       <c r="G40" t="n">
-        <v>553.847900390625</v>
+        <v>553.847961425781</v>
       </c>
       <c r="H40" t="n">
         <v>208</v>
@@ -1616,7 +1616,7 @@
         <v>606.5</v>
       </c>
       <c r="G43" t="n">
-        <v>555.221130371094</v>
+        <v>555.221069335938</v>
       </c>
       <c r="H43" t="n">
         <v>116</v>
@@ -1790,7 +1790,7 @@
         <v>605</v>
       </c>
       <c r="G49" t="n">
-        <v>553.847900390625</v>
+        <v>553.847961425781</v>
       </c>
       <c r="H49" t="n">
         <v>21</v>
@@ -1964,7 +1964,7 @@
         <v>644</v>
       </c>
       <c r="G55" t="n">
-        <v>589.550537109375</v>
+        <v>589.550476074219</v>
       </c>
       <c r="H55" t="n">
         <v>220</v>
@@ -1993,7 +1993,7 @@
         <v>647.5</v>
       </c>
       <c r="G56" t="n">
-        <v>592.754638671875</v>
+        <v>592.754577636719</v>
       </c>
       <c r="H56" t="n">
         <v>210</v>
@@ -2022,7 +2022,7 @@
         <v>640</v>
       </c>
       <c r="G57" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H57" t="n">
         <v>131</v>
@@ -2167,7 +2167,7 @@
         <v>630.5</v>
       </c>
       <c r="G62" t="n">
-        <v>577.191955566406</v>
+        <v>577.19189453125</v>
       </c>
       <c r="H62" t="n">
         <v>666</v>
@@ -2225,7 +2225,7 @@
         <v>625</v>
       </c>
       <c r="G64" t="n">
-        <v>572.156982421875</v>
+        <v>572.156921386719</v>
       </c>
       <c r="H64" t="n">
         <v>75</v>
@@ -2254,7 +2254,7 @@
         <v>632</v>
       </c>
       <c r="G65" t="n">
-        <v>578.565063476562</v>
+        <v>578.565124511719</v>
       </c>
       <c r="H65" t="n">
         <v>36</v>
@@ -2312,7 +2312,7 @@
         <v>626</v>
       </c>
       <c r="G67" t="n">
-        <v>573.072448730469</v>
+        <v>573.072387695312</v>
       </c>
       <c r="H67" t="n">
         <v>153</v>
@@ -2370,7 +2370,7 @@
         <v>634</v>
       </c>
       <c r="G69" t="n">
-        <v>580.396057128906</v>
+        <v>580.39599609375</v>
       </c>
       <c r="H69" t="n">
         <v>149</v>
@@ -2457,7 +2457,7 @@
         <v>638.5</v>
       </c>
       <c r="G72" t="n">
-        <v>584.515563964844</v>
+        <v>584.515502929688</v>
       </c>
       <c r="H72" t="n">
         <v>149</v>
@@ -2486,7 +2486,7 @@
         <v>635.5</v>
       </c>
       <c r="G73" t="n">
-        <v>581.769165039062</v>
+        <v>581.769226074219</v>
       </c>
       <c r="H73" t="n">
         <v>46</v>
@@ -2515,7 +2515,7 @@
         <v>626.5</v>
       </c>
       <c r="G74" t="n">
-        <v>573.530090332031</v>
+        <v>573.530151367188</v>
       </c>
       <c r="H74" t="n">
         <v>71</v>
@@ -2573,7 +2573,7 @@
         <v>640</v>
       </c>
       <c r="G76" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H76" t="n">
         <v>170</v>
@@ -2602,7 +2602,7 @@
         <v>640</v>
       </c>
       <c r="G77" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H77" t="n">
         <v>239</v>
@@ -2660,7 +2660,7 @@
         <v>635.5</v>
       </c>
       <c r="G79" t="n">
-        <v>581.769165039062</v>
+        <v>581.769226074219</v>
       </c>
       <c r="H79" t="n">
         <v>48</v>
@@ -2718,7 +2718,7 @@
         <v>640</v>
       </c>
       <c r="G81" t="n">
-        <v>585.888671875</v>
+        <v>585.888732910156</v>
       </c>
       <c r="H81" t="n">
         <v>96</v>
@@ -3066,7 +3066,7 @@
         <v>662.5</v>
       </c>
       <c r="G93" t="n">
-        <v>606.486389160156</v>
+        <v>606.486328125</v>
       </c>
       <c r="H93" t="n">
         <v>359</v>
@@ -80139,7 +80139,7 @@
         <v>0.0124000003561378</v>
       </c>
       <c r="D2751" t="n">
-        <v>0.0136000001803041</v>
+        <v>0.0149999996647239</v>
       </c>
       <c r="E2751" t="n">
         <v>0.0120000001043081</v>
@@ -80154,6 +80154,35 @@
         <v>29310965</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>0.015599999576807</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>0.017000000923872</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>0.0149999996647239</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>0.0175999999046326</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>54986021</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -80168,7 +80168,7 @@
         <v>0.015599999576807</v>
       </c>
       <c r="D2752" t="n">
-        <v>0.017000000923872</v>
+        <v>0.0175999999046326</v>
       </c>
       <c r="E2752" t="n">
         <v>0.0149999996647239</v>
@@ -80180,9 +80180,38 @@
         <v>0.0175999999046326</v>
       </c>
       <c r="H2752" t="n">
-        <v>54986021</v>
+        <v>55136021</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>0.0204000007361174</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>0.0179999992251396</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>0.0192000009119511</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>76334385</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FDA.MI.xlsx
+++ b/data/FDA.MI.xlsx
@@ -427,7 +427,7 @@
         <v>634</v>
       </c>
       <c r="G2" t="n">
-        <v>580.39599609375</v>
+        <v>580.396057128906</v>
       </c>
       <c r="H2" t="n">
         <v>141</v>
@@ -456,7 +456,7 @@
         <v>634</v>
       </c>
       <c r="G3" t="n">
-        <v>580.39599609375</v>
+        <v>580.396057128906</v>
       </c>
       <c r="H3" t="n">
         <v>82</v>
@@ -775,7 +775,7 @@
         <v>471.399993896484</v>
       </c>
       <c r="G14" t="n">
-        <v>431.543670654297</v>
+        <v>431.543640136719</v>
       </c>
       <c r="H14" t="n">
         <v>535</v>
@@ -978,7 +978,7 @@
         <v>529</v>
       </c>
       <c r="G21" t="n">
-        <v>484.273651123047</v>
+        <v>484.273620605469</v>
       </c>
       <c r="H21" t="n">
         <v>70</v>
@@ -1036,7 +1036,7 @@
         <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>448.571075439453</v>
+        <v>448.571044921875</v>
       </c>
       <c r="H23" t="n">
         <v>79</v>
@@ -1268,7 +1268,7 @@
         <v>559</v>
       </c>
       <c r="G31" t="n">
-        <v>511.737182617188</v>
+        <v>511.737152099609</v>
       </c>
       <c r="H31" t="n">
         <v>324</v>
@@ -1326,7 +1326,7 @@
         <v>594.5</v>
       </c>
       <c r="G33" t="n">
-        <v>544.235717773438</v>
+        <v>544.235656738281</v>
       </c>
       <c r="H33" t="n">
         <v>417</v>
@@ -1442,7 +1442,7 @@
         <v>616</v>
       </c>
       <c r="G37" t="n">
-        <v>563.917846679688</v>
+        <v>563.917907714844</v>
       </c>
       <c r="H37" t="n">
         <v>276</v>
@@ -1529,7 +1529,7 @@
         <v>605</v>
       </c>
       <c r="G40" t="n">
-        <v>553.847961425781</v>
+        <v>553.847900390625</v>
       </c>
       <c r="H40" t="n">
         <v>208</v>
@@ -1616,7 +1616,7 @@
         <v>606.5</v>
       </c>
       <c r="G43" t="n">
-        <v>555.221069335938</v>
+        <v>555.221130371094</v>
       </c>
       <c r="H43" t="n">
         <v>116</v>
@@ -1790,7 +1790,7 @@
         <v>605</v>
       </c>
       <c r="G49" t="n">
-        <v>553.847961425781</v>
+        <v>553.847900390625</v>
       </c>
       <c r="H49" t="n">
         <v>21</v>
@@ -1964,7 +1964,7 @@
         <v>644</v>
       </c>
       <c r="G55" t="n">
-        <v>589.550476074219</v>
+        <v>589.550537109375</v>
       </c>
       <c r="H55" t="n">
         <v>220</v>
@@ -1993,7 +1993,7 @@
         <v>647.5</v>
       </c>
       <c r="G56" t="n">
-        <v>592.754577636719</v>
+        <v>592.754638671875</v>
       </c>
       <c r="H56" t="n">
         <v>210</v>
@@ -2022,7 +2022,7 @@
         <v>640</v>
       </c>
       <c r="G57" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H57" t="n">
         <v>131</v>
@@ -2167,7 +2167,7 @@
         <v>630.5</v>
       </c>
       <c r="G62" t="n">
-        <v>577.19189453125</v>
+        <v>577.191955566406</v>
       </c>
       <c r="H62" t="n">
         <v>666</v>
@@ -2225,7 +2225,7 @@
         <v>625</v>
       </c>
       <c r="G64" t="n">
-        <v>572.156921386719</v>
+        <v>572.156982421875</v>
       </c>
       <c r="H64" t="n">
         <v>75</v>
@@ -2254,7 +2254,7 @@
         <v>632</v>
       </c>
       <c r="G65" t="n">
-        <v>578.565124511719</v>
+        <v>578.565063476562</v>
       </c>
       <c r="H65" t="n">
         <v>36</v>
@@ -2312,7 +2312,7 @@
         <v>626</v>
       </c>
       <c r="G67" t="n">
-        <v>573.072387695312</v>
+        <v>573.072448730469</v>
       </c>
       <c r="H67" t="n">
         <v>153</v>
@@ -2370,7 +2370,7 @@
         <v>634</v>
       </c>
       <c r="G69" t="n">
-        <v>580.39599609375</v>
+        <v>580.396057128906</v>
       </c>
       <c r="H69" t="n">
         <v>149</v>
@@ -2457,7 +2457,7 @@
         <v>638.5</v>
       </c>
       <c r="G72" t="n">
-        <v>584.515502929688</v>
+        <v>584.515563964844</v>
       </c>
       <c r="H72" t="n">
         <v>149</v>
@@ -2486,7 +2486,7 @@
         <v>635.5</v>
       </c>
       <c r="G73" t="n">
-        <v>581.769226074219</v>
+        <v>581.769165039062</v>
       </c>
       <c r="H73" t="n">
         <v>46</v>
@@ -2515,7 +2515,7 @@
         <v>626.5</v>
       </c>
       <c r="G74" t="n">
-        <v>573.530151367188</v>
+        <v>573.530090332031</v>
       </c>
       <c r="H74" t="n">
         <v>71</v>
@@ -2573,7 +2573,7 @@
         <v>640</v>
       </c>
       <c r="G76" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H76" t="n">
         <v>170</v>
@@ -2602,7 +2602,7 @@
         <v>640</v>
       </c>
       <c r="G77" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H77" t="n">
         <v>239</v>
@@ -2660,7 +2660,7 @@
         <v>635.5</v>
       </c>
       <c r="G79" t="n">
-        <v>581.769226074219</v>
+        <v>581.769165039062</v>
       </c>
       <c r="H79" t="n">
         <v>48</v>
@@ -2718,7 +2718,7 @@
         <v>640</v>
       </c>
       <c r="G81" t="n">
-        <v>585.888732910156</v>
+        <v>585.888671875</v>
       </c>
       <c r="H81" t="n">
         <v>96</v>
@@ -3066,7 +3066,7 @@
         <v>662.5</v>
       </c>
       <c r="G93" t="n">
-        <v>606.486328125</v>
+        <v>606.486389160156</v>
       </c>
       <c r="H93" t="n">
         <v>359</v>
@@ -80212,6 +80212,35 @@
         <v>76334385</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>0.0196000002324581</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>0.0177999995648861</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>0.0184000004082918</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>46439477</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
